--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2261"/>
+  <dimension ref="A1:E2284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43395,6 +43395,443 @@
         <v>283.9445833333332</v>
       </c>
     </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B2262" t="n">
+        <v>342.1470833333333</v>
+      </c>
+      <c r="C2262" t="n">
+        <v>511.3220833333333</v>
+      </c>
+      <c r="D2262" t="n">
+        <v>224.1229166666667</v>
+      </c>
+      <c r="E2262" t="n">
+        <v>224.1166666666667</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="B2263" t="n">
+        <v>293.5304166666667</v>
+      </c>
+      <c r="C2263" t="n">
+        <v>472.7250000000001</v>
+      </c>
+      <c r="D2263" t="n">
+        <v>158.2033333333333</v>
+      </c>
+      <c r="E2263" t="n">
+        <v>158.1975</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="B2264" t="n">
+        <v>266.4958333333333</v>
+      </c>
+      <c r="C2264" t="n">
+        <v>483.1641666666669</v>
+      </c>
+      <c r="D2264" t="n">
+        <v>176.3345833333333</v>
+      </c>
+      <c r="E2264" t="n">
+        <v>176.33</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="B2265" t="n">
+        <v>323.9299999999999</v>
+      </c>
+      <c r="C2265" t="n">
+        <v>478.6595833333334</v>
+      </c>
+      <c r="D2265" t="n">
+        <v>290.36125</v>
+      </c>
+      <c r="E2265" t="n">
+        <v>290.355</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B2266" t="n">
+        <v>267.1708333333333</v>
+      </c>
+      <c r="C2266" t="n">
+        <v>279.73625</v>
+      </c>
+      <c r="D2266" t="n">
+        <v>264.6304166666667</v>
+      </c>
+      <c r="E2266" t="n">
+        <v>264.6245833333333</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B2267" t="n">
+        <v>220.0320833333333</v>
+      </c>
+      <c r="C2267" t="n">
+        <v>225.9070833333333</v>
+      </c>
+      <c r="D2267" t="n">
+        <v>220.0324999999999</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>220.0266666666667</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="B2268" t="n">
+        <v>282.1691666666666</v>
+      </c>
+      <c r="C2268" t="n">
+        <v>457.7491666666668</v>
+      </c>
+      <c r="D2268" t="n">
+        <v>271.1891666666666</v>
+      </c>
+      <c r="E2268" t="n">
+        <v>271.1829166666667</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B2269" t="n">
+        <v>325.8879166666666</v>
+      </c>
+      <c r="C2269" t="n">
+        <v>554.2287500000001</v>
+      </c>
+      <c r="D2269" t="n">
+        <v>256.2695833333333</v>
+      </c>
+      <c r="E2269" t="n">
+        <v>256.2625</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B2270" t="n">
+        <v>372.22625</v>
+      </c>
+      <c r="C2270" t="n">
+        <v>561.0433333333332</v>
+      </c>
+      <c r="D2270" t="n">
+        <v>335.79875</v>
+      </c>
+      <c r="E2270" t="n">
+        <v>335.7929166666666</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B2271" t="n">
+        <v>379.5195833333333</v>
+      </c>
+      <c r="C2271" t="n">
+        <v>533.5112500000001</v>
+      </c>
+      <c r="D2271" t="n">
+        <v>347.0091666666667</v>
+      </c>
+      <c r="E2271" t="n">
+        <v>347.0016666666666</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B2272" t="n">
+        <v>338.82875</v>
+      </c>
+      <c r="C2272" t="n">
+        <v>453.9449999999999</v>
+      </c>
+      <c r="D2272" t="n">
+        <v>300.6904166666666</v>
+      </c>
+      <c r="E2272" t="n">
+        <v>300.6854166666666</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="B2273" t="n">
+        <v>241.7320833333333</v>
+      </c>
+      <c r="C2273" t="n">
+        <v>339.6333333333334</v>
+      </c>
+      <c r="D2273" t="n">
+        <v>241.72875</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>241.7225</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="B2274" t="n">
+        <v>238.8341666666667</v>
+      </c>
+      <c r="C2274" t="n">
+        <v>277.3329166666666</v>
+      </c>
+      <c r="D2274" t="n">
+        <v>238.8333333333333</v>
+      </c>
+      <c r="E2274" t="n">
+        <v>238.8275</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="B2275" t="n">
+        <v>359.1095833333333</v>
+      </c>
+      <c r="C2275" t="n">
+        <v>556.7241666666667</v>
+      </c>
+      <c r="D2275" t="n">
+        <v>341.8458333333333</v>
+      </c>
+      <c r="E2275" t="n">
+        <v>341.8391666666666</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B2276" t="n">
+        <v>330.3270833333333</v>
+      </c>
+      <c r="C2276" t="n">
+        <v>474.1383333333333</v>
+      </c>
+      <c r="D2276" t="n">
+        <v>309.2520833333334</v>
+      </c>
+      <c r="E2276" t="n">
+        <v>309.24625</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="B2277" t="n">
+        <v>326.0858333333334</v>
+      </c>
+      <c r="C2277" t="n">
+        <v>413.6120833333334</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>249.2470833333333</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>249.2404166666666</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="B2278" t="n">
+        <v>269.1958333333333</v>
+      </c>
+      <c r="C2278" t="n">
+        <v>383.6241666666667</v>
+      </c>
+      <c r="D2278" t="n">
+        <v>181.0579166666666</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>181.0516666666666</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="B2279" t="n">
+        <v>273.5766666666667</v>
+      </c>
+      <c r="C2279" t="n">
+        <v>387.8241666666667</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>152.86625</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>152.8608333333333</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="B2280" t="n">
+        <v>178.0883333333333</v>
+      </c>
+      <c r="C2280" t="n">
+        <v>209.46375</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>144.8695833333333</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>144.86375</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>29/03/2026</t>
+        </is>
+      </c>
+      <c r="B2281" t="n">
+        <v>143.7866666666666</v>
+      </c>
+      <c r="C2281" t="n">
+        <v>166.0616666666667</v>
+      </c>
+      <c r="D2281" t="n">
+        <v>143.7841666666666</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>143.7791666666667</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="B2282" t="n">
+        <v>400.6091666666666</v>
+      </c>
+      <c r="C2282" t="n">
+        <v>511.02125</v>
+      </c>
+      <c r="D2282" t="n">
+        <v>390.6929166666666</v>
+      </c>
+      <c r="E2282" t="n">
+        <v>390.6875000000001</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="B2283" t="n">
+        <v>256.7008333333333</v>
+      </c>
+      <c r="C2283" t="n">
+        <v>335.68</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>251.675</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>251.6670833333334</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B2284" t="n">
+        <v>327.3191666666667</v>
+      </c>
+      <c r="C2284" t="n">
+        <v>405.5191666666666</v>
+      </c>
+      <c r="D2284" t="n">
+        <v>304.3904166666667</v>
+      </c>
+      <c r="E2284" t="n">
+        <v>304.3841666666667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2284"/>
+  <dimension ref="A1:E2289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43832,6 +43832,101 @@
         <v>304.3841666666667</v>
       </c>
     </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B2285" t="n">
+        <v>234.01625</v>
+      </c>
+      <c r="C2285" t="n">
+        <v>298.2762500000001</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>174.93</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>174.92375</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B2286" t="n">
+        <v>197.26875</v>
+      </c>
+      <c r="C2286" t="n">
+        <v>215.41875</v>
+      </c>
+      <c r="D2286" t="n">
+        <v>190.13875</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>190.13625</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B2287" t="n">
+        <v>143.5791666666667</v>
+      </c>
+      <c r="C2287" t="n">
+        <v>211.2958333333333</v>
+      </c>
+      <c r="D2287" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B2288" t="n">
+        <v>139.8283333333333</v>
+      </c>
+      <c r="C2288" t="n">
+        <v>147.0604166666666</v>
+      </c>
+      <c r="D2288" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2288" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B2289" t="n">
+        <v>191.82625</v>
+      </c>
+      <c r="C2289" t="n">
+        <v>261.0170833333333</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>81.91374999999998</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>81.91041666666665</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2289"/>
+  <dimension ref="A1:E2296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43927,6 +43927,139 @@
         <v>81.91041666666665</v>
       </c>
     </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B2290" t="n">
+        <v>247.3441666666666</v>
+      </c>
+      <c r="C2290" t="n">
+        <v>340.89625</v>
+      </c>
+      <c r="D2290" t="n">
+        <v>138.4554166666667</v>
+      </c>
+      <c r="E2290" t="n">
+        <v>138.6070833333333</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B2291" t="n">
+        <v>273.81125</v>
+      </c>
+      <c r="C2291" t="n">
+        <v>329.2804166666667</v>
+      </c>
+      <c r="D2291" t="n">
+        <v>181.0916666666667</v>
+      </c>
+      <c r="E2291" t="n">
+        <v>181.0866666666667</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B2292" t="n">
+        <v>286.5541666666666</v>
+      </c>
+      <c r="C2292" t="n">
+        <v>315.7662500000001</v>
+      </c>
+      <c r="D2292" t="n">
+        <v>239.8470833333333</v>
+      </c>
+      <c r="E2292" t="n">
+        <v>239.8395833333333</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B2293" t="n">
+        <v>267.0270833333333</v>
+      </c>
+      <c r="C2293" t="n">
+        <v>281.9591666666667</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>242.4699999999999</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>242.4629166666666</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B2294" t="n">
+        <v>153.5729166666667</v>
+      </c>
+      <c r="C2294" t="n">
+        <v>158.6458333333333</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B2295" t="n">
+        <v>119.3404166666666</v>
+      </c>
+      <c r="C2295" t="n">
+        <v>131.7295833333334</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>61.8095833333333</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>61.80874999999997</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B2296" t="n">
+        <v>165.7791666666667</v>
+      </c>
+      <c r="C2296" t="n">
+        <v>223.4283333333333</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>129.7758333333333</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>130.4854166666666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2296"/>
+  <dimension ref="A1:E2495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44060,6 +44060,3787 @@
         <v>130.4854166666666</v>
       </c>
     </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B2297" t="n">
+        <v>188.5695833333333</v>
+      </c>
+      <c r="C2297" t="n">
+        <v>243.5816666666667</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>144.7254166666666</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>145.8925</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B2298" t="n">
+        <v>204.5875</v>
+      </c>
+      <c r="C2298" t="n">
+        <v>239.745</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>183.0608333333334</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>188.4762500000001</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B2299" t="n">
+        <v>210.1170833333333</v>
+      </c>
+      <c r="C2299" t="n">
+        <v>241.8991666666667</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>199.485</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>199.61625</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B2300" t="n">
+        <v>199.7975</v>
+      </c>
+      <c r="C2300" t="n">
+        <v>225.43375</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>193.5283333333333</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>193.6641666666667</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B2301" t="n">
+        <v>167.8191666666666</v>
+      </c>
+      <c r="C2301" t="n">
+        <v>186.0529166666667</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>135.5191666666667</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>135.5145833333333</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B2302" t="n">
+        <v>174.1095833333333</v>
+      </c>
+      <c r="C2302" t="n">
+        <v>179.3191666666667</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>173.5695833333333</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>173.5654166666667</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B2303" t="n">
+        <v>201.1045833333333</v>
+      </c>
+      <c r="C2303" t="n">
+        <v>242.5554166666667</v>
+      </c>
+      <c r="D2303" t="n">
+        <v>189.9370833333333</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>189.9329166666667</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B2304" t="n">
+        <v>183.4816666666667</v>
+      </c>
+      <c r="C2304" t="n">
+        <v>238.19625</v>
+      </c>
+      <c r="D2304" t="n">
+        <v>170.2179166666666</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>170.2149999999999</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B2305" t="n">
+        <v>209.525</v>
+      </c>
+      <c r="C2305" t="n">
+        <v>250.2579166666666</v>
+      </c>
+      <c r="D2305" t="n">
+        <v>122.4458333333333</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>122.44375</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B2306" t="n">
+        <v>197.0991666666666</v>
+      </c>
+      <c r="C2306" t="n">
+        <v>245.38875</v>
+      </c>
+      <c r="D2306" t="n">
+        <v>122.63875</v>
+      </c>
+      <c r="E2306" t="n">
+        <v>123.9404166666667</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B2307" t="n">
+        <v>227.3666666666667</v>
+      </c>
+      <c r="C2307" t="n">
+        <v>258.9170833333333</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>207.7916666666666</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>208.0233333333334</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B2308" t="n">
+        <v>214.0416666666666</v>
+      </c>
+      <c r="C2308" t="n">
+        <v>297.24875</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>93.44083333333332</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>93.43624999999997</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B2309" t="n">
+        <v>192.6295833333334</v>
+      </c>
+      <c r="C2309" t="n">
+        <v>221.4566666666667</v>
+      </c>
+      <c r="D2309" t="n">
+        <v>60.42333333333332</v>
+      </c>
+      <c r="E2309" t="n">
+        <v>60.42166666666665</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B2310" t="n">
+        <v>246.5016666666667</v>
+      </c>
+      <c r="C2310" t="n">
+        <v>302.3829166666666</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>73.90416666666665</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>73.90041666666666</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B2311" t="n">
+        <v>253.4333333333333</v>
+      </c>
+      <c r="C2311" t="n">
+        <v>306.4183333333334</v>
+      </c>
+      <c r="D2311" t="n">
+        <v>65.10374999999998</v>
+      </c>
+      <c r="E2311" t="n">
+        <v>65.10333333333331</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B2312" t="n">
+        <v>256.9183333333334</v>
+      </c>
+      <c r="C2312" t="n">
+        <v>309.9508333333334</v>
+      </c>
+      <c r="D2312" t="n">
+        <v>60.14749999999997</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>60.14791666666664</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B2313" t="n">
+        <v>266.97375</v>
+      </c>
+      <c r="C2313" t="n">
+        <v>311.9195833333333</v>
+      </c>
+      <c r="D2313" t="n">
+        <v>65.66416666666666</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>65.66416666666665</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B2314" t="n">
+        <v>211.9191666666667</v>
+      </c>
+      <c r="C2314" t="n">
+        <v>216.18625</v>
+      </c>
+      <c r="D2314" t="n">
+        <v>58.52916666666664</v>
+      </c>
+      <c r="E2314" t="n">
+        <v>58.52916666666664</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B2315" t="n">
+        <v>241.9870833333333</v>
+      </c>
+      <c r="C2315" t="n">
+        <v>241.9920833333333</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>90.46124999999999</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>90.45875000000001</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B2316" t="n">
+        <v>185.8641666666666</v>
+      </c>
+      <c r="C2316" t="n">
+        <v>185.8674999999999</v>
+      </c>
+      <c r="D2316" t="n">
+        <v>74.21708333333332</v>
+      </c>
+      <c r="E2316" t="n">
+        <v>74.21666666666665</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B2317" t="n">
+        <v>299.8616666666667</v>
+      </c>
+      <c r="C2317" t="n">
+        <v>368.85125</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>68.27041666666666</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>68.27249999999999</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B2318" t="n">
+        <v>310.25625</v>
+      </c>
+      <c r="C2318" t="n">
+        <v>369.8570833333333</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>67.42208333333332</v>
+      </c>
+      <c r="E2318" t="n">
+        <v>67.42333333333332</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B2319" t="n">
+        <v>319.3970833333333</v>
+      </c>
+      <c r="C2319" t="n">
+        <v>382.955</v>
+      </c>
+      <c r="D2319" t="n">
+        <v>68.56874999999998</v>
+      </c>
+      <c r="E2319" t="n">
+        <v>68.56916666666665</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B2320" t="n">
+        <v>306.5604166666667</v>
+      </c>
+      <c r="C2320" t="n">
+        <v>380.7804166666667</v>
+      </c>
+      <c r="D2320" t="n">
+        <v>80.86166666666666</v>
+      </c>
+      <c r="E2320" t="n">
+        <v>80.86083333333333</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B2321" t="n">
+        <v>319.9341666666667</v>
+      </c>
+      <c r="C2321" t="n">
+        <v>382.3020833333333</v>
+      </c>
+      <c r="D2321" t="n">
+        <v>182.7558333333333</v>
+      </c>
+      <c r="E2321" t="n">
+        <v>182.7529166666667</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B2322" t="n">
+        <v>193.0637499999999</v>
+      </c>
+      <c r="C2322" t="n">
+        <v>199.29375</v>
+      </c>
+      <c r="D2322" t="n">
+        <v>192.4695833333333</v>
+      </c>
+      <c r="E2322" t="n">
+        <v>192.4695833333333</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B2323" t="n">
+        <v>163.7979166666667</v>
+      </c>
+      <c r="C2323" t="n">
+        <v>163.8016666666666</v>
+      </c>
+      <c r="D2323" t="n">
+        <v>163.795</v>
+      </c>
+      <c r="E2323" t="n">
+        <v>163.7945833333333</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B2324" t="n">
+        <v>213.2954166666666</v>
+      </c>
+      <c r="C2324" t="n">
+        <v>227.93375</v>
+      </c>
+      <c r="D2324" t="n">
+        <v>213.29125</v>
+      </c>
+      <c r="E2324" t="n">
+        <v>213.2904166666666</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2325" t="n">
+        <v>193.6683333333334</v>
+      </c>
+      <c r="C2325" t="n">
+        <v>212.6341666666666</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>184.8770833333333</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>193.1291666666667</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B2326" t="n">
+        <v>201.9945833333333</v>
+      </c>
+      <c r="C2326" t="n">
+        <v>239.0608333333332</v>
+      </c>
+      <c r="D2326" t="n">
+        <v>190.2845833333333</v>
+      </c>
+      <c r="E2326" t="n">
+        <v>200.7829166666667</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B2327" t="n">
+        <v>202.9366666666667</v>
+      </c>
+      <c r="C2327" t="n">
+        <v>244.7887500000001</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>188.5325</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>202.195</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B2328" t="n">
+        <v>229.565</v>
+      </c>
+      <c r="C2328" t="n">
+        <v>265.8429166666667</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>217.5583333333333</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>228.4587499999999</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B2329" t="n">
+        <v>149.73125</v>
+      </c>
+      <c r="C2329" t="n">
+        <v>149.7358333333333</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>149.7287499999999</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>149.7258333333333</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B2330" t="n">
+        <v>127.315</v>
+      </c>
+      <c r="C2330" t="n">
+        <v>127.3191666666667</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>126.9575</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>126.9575</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B2331" t="n">
+        <v>201.2175</v>
+      </c>
+      <c r="C2331" t="n">
+        <v>214.8345833333334</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>194.1929166666666</v>
+      </c>
+      <c r="E2331" t="n">
+        <v>194.1929166666667</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2332" t="n">
+        <v>188.3041666666667</v>
+      </c>
+      <c r="C2332" t="n">
+        <v>207.6766666666666</v>
+      </c>
+      <c r="D2332" t="n">
+        <v>179.4354166666666</v>
+      </c>
+      <c r="E2332" t="n">
+        <v>179.4354166666667</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B2333" t="n">
+        <v>180.8608333333334</v>
+      </c>
+      <c r="C2333" t="n">
+        <v>200.0479166666666</v>
+      </c>
+      <c r="D2333" t="n">
+        <v>168.25625</v>
+      </c>
+      <c r="E2333" t="n">
+        <v>170.5879166666666</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B2334" t="n">
+        <v>192.9629166666666</v>
+      </c>
+      <c r="C2334" t="n">
+        <v>205.52125</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>183.1454166666666</v>
+      </c>
+      <c r="E2334" t="n">
+        <v>183.9154166666667</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B2335" t="n">
+        <v>179.84375</v>
+      </c>
+      <c r="C2335" t="n">
+        <v>204.0558333333333</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>166.7208333333333</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>174.1958333333333</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B2336" t="n">
+        <v>141.52</v>
+      </c>
+      <c r="C2336" t="n">
+        <v>156.04375</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>123.1875</v>
+      </c>
+      <c r="E2336" t="n">
+        <v>125.4495833333333</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B2337" t="n">
+        <v>190.3075</v>
+      </c>
+      <c r="C2337" t="n">
+        <v>190.3129166666667</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>190.0920833333333</v>
+      </c>
+      <c r="E2337" t="n">
+        <v>190.095</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B2338" t="n">
+        <v>225.47125</v>
+      </c>
+      <c r="C2338" t="n">
+        <v>269.2699999999999</v>
+      </c>
+      <c r="D2338" t="n">
+        <v>220.2408333333333</v>
+      </c>
+      <c r="E2338" t="n">
+        <v>224.3720833333333</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B2339" t="n">
+        <v>266.25625</v>
+      </c>
+      <c r="C2339" t="n">
+        <v>297.1795833333334</v>
+      </c>
+      <c r="D2339" t="n">
+        <v>254.6920833333333</v>
+      </c>
+      <c r="E2339" t="n">
+        <v>261.4104166666667</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B2340" t="n">
+        <v>263.815</v>
+      </c>
+      <c r="C2340" t="n">
+        <v>295.0154166666667</v>
+      </c>
+      <c r="D2340" t="n">
+        <v>263.4970833333334</v>
+      </c>
+      <c r="E2340" t="n">
+        <v>263.51875</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B2341" t="n">
+        <v>263.7129166666667</v>
+      </c>
+      <c r="C2341" t="n">
+        <v>292.88875</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>253.18125</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>259.8491666666666</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B2342" t="n">
+        <v>272.85125</v>
+      </c>
+      <c r="C2342" t="n">
+        <v>299.0191666666666</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>269.0116666666667</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>270.9204166666667</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B2343" t="n">
+        <v>220.2208333333332</v>
+      </c>
+      <c r="C2343" t="n">
+        <v>220.2208333333332</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>220.2208333333332</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>220.2208333333332</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B2344" t="n">
+        <v>163.0783333333333</v>
+      </c>
+      <c r="C2344" t="n">
+        <v>163.0820833333333</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>163.0741666666666</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>163.0791666666666</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B2345" t="n">
+        <v>222.9216666666667</v>
+      </c>
+      <c r="C2345" t="n">
+        <v>225.9904166666667</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>222.9154166666667</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>222.9208333333333</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B2346" t="n">
+        <v>205.8670833333333</v>
+      </c>
+      <c r="C2346" t="n">
+        <v>217.2058333333333</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>205.8591666666667</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>205.86625</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B2347" t="n">
+        <v>199.5329166666666</v>
+      </c>
+      <c r="C2347" t="n">
+        <v>211.4708333333333</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>193.53875</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>197.0925</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B2348" t="n">
+        <v>166.3495833333333</v>
+      </c>
+      <c r="C2348" t="n">
+        <v>166.3520833333333</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>166.3445833333333</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>166.3504166666667</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B2349" t="n">
+        <v>183.16</v>
+      </c>
+      <c r="C2349" t="n">
+        <v>198.7525</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>178.63375</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>183.16125</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B2350" t="n">
+        <v>175.4345833333333</v>
+      </c>
+      <c r="C2350" t="n">
+        <v>175.4383333333333</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>175.4283333333333</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>175.435</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B2351" t="n">
+        <v>163.2358333333333</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>163.2366666666667</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>163.2320833333333</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>163.2375</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B2352" t="n">
+        <v>194.585</v>
+      </c>
+      <c r="C2352" t="n">
+        <v>219.9866666666667</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>192.4645833333333</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>193.2679166666667</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B2353" t="n">
+        <v>204.0370833333334</v>
+      </c>
+      <c r="C2353" t="n">
+        <v>227.8091666666666</v>
+      </c>
+      <c r="D2353" t="n">
+        <v>197.0695833333334</v>
+      </c>
+      <c r="E2353" t="n">
+        <v>201.2975</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B2354" t="n">
+        <v>233.9791666666667</v>
+      </c>
+      <c r="C2354" t="n">
+        <v>234.2058333333334</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>233.9716666666667</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>233.9779166666667</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B2355" t="n">
+        <v>234.1566666666667</v>
+      </c>
+      <c r="C2355" t="n">
+        <v>234.2245833333334</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>231.2120833333333</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>233.8966666666666</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B2356" t="n">
+        <v>234.0062500000001</v>
+      </c>
+      <c r="C2356" t="n">
+        <v>234.0329166666667</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>227.36625</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>232.3716666666667</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B2357" t="n">
+        <v>177.1916666666666</v>
+      </c>
+      <c r="C2357" t="n">
+        <v>177.195</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>177.1870833333333</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>177.1941666666667</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B2358" t="n">
+        <v>153.6666666666667</v>
+      </c>
+      <c r="C2358" t="n">
+        <v>153.6683333333333</v>
+      </c>
+      <c r="D2358" t="n">
+        <v>153.6633333333333</v>
+      </c>
+      <c r="E2358" t="n">
+        <v>153.6683333333333</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B2359" t="n">
+        <v>206.4820833333333</v>
+      </c>
+      <c r="C2359" t="n">
+        <v>206.4854166666667</v>
+      </c>
+      <c r="D2359" t="n">
+        <v>206.4741666666667</v>
+      </c>
+      <c r="E2359" t="n">
+        <v>206.4808333333334</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B2360" t="n">
+        <v>204.79125</v>
+      </c>
+      <c r="C2360" t="n">
+        <v>204.7941666666667</v>
+      </c>
+      <c r="D2360" t="n">
+        <v>204.7833333333334</v>
+      </c>
+      <c r="E2360" t="n">
+        <v>204.7891666666667</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B2361" t="n">
+        <v>207.1679166666667</v>
+      </c>
+      <c r="C2361" t="n">
+        <v>207.17125</v>
+      </c>
+      <c r="D2361" t="n">
+        <v>207.1633333333333</v>
+      </c>
+      <c r="E2361" t="n">
+        <v>207.1683333333333</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B2362" t="n">
+        <v>200.8583333333333</v>
+      </c>
+      <c r="C2362" t="n">
+        <v>202.51375</v>
+      </c>
+      <c r="D2362" t="n">
+        <v>200.8516666666667</v>
+      </c>
+      <c r="E2362" t="n">
+        <v>200.8570833333333</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B2363" t="n">
+        <v>179.8975</v>
+      </c>
+      <c r="C2363" t="n">
+        <v>201.80875</v>
+      </c>
+      <c r="D2363" t="n">
+        <v>172.4633333333333</v>
+      </c>
+      <c r="E2363" t="n">
+        <v>176.4270833333333</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B2364" t="n">
+        <v>192.4058333333333</v>
+      </c>
+      <c r="C2364" t="n">
+        <v>214.7033333333333</v>
+      </c>
+      <c r="D2364" t="n">
+        <v>192.4029166666667</v>
+      </c>
+      <c r="E2364" t="n">
+        <v>192.41</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B2365" t="n">
+        <v>171.1666666666667</v>
+      </c>
+      <c r="C2365" t="n">
+        <v>171.1675</v>
+      </c>
+      <c r="D2365" t="n">
+        <v>171.16375</v>
+      </c>
+      <c r="E2365" t="n">
+        <v>171.1704166666667</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B2366" t="n">
+        <v>203.9187499999999</v>
+      </c>
+      <c r="C2366" t="n">
+        <v>225.8475</v>
+      </c>
+      <c r="D2366" t="n">
+        <v>203.9125</v>
+      </c>
+      <c r="E2366" t="n">
+        <v>203.9199999999999</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B2367" t="n">
+        <v>203.1791666666667</v>
+      </c>
+      <c r="C2367" t="n">
+        <v>203.1820833333334</v>
+      </c>
+      <c r="D2367" t="n">
+        <v>192.55125</v>
+      </c>
+      <c r="E2367" t="n">
+        <v>199.3725</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2368" t="n">
+        <v>207.755</v>
+      </c>
+      <c r="C2368" t="n">
+        <v>209.8595833333333</v>
+      </c>
+      <c r="D2368" t="n">
+        <v>194.1466666666666</v>
+      </c>
+      <c r="E2368" t="n">
+        <v>202.3729166666667</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2369" t="n">
+        <v>200.8354166666667</v>
+      </c>
+      <c r="C2369" t="n">
+        <v>204.6845833333333</v>
+      </c>
+      <c r="D2369" t="n">
+        <v>177.8675</v>
+      </c>
+      <c r="E2369" t="n">
+        <v>194.0954166666667</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2370" t="n">
+        <v>199.98875</v>
+      </c>
+      <c r="C2370" t="n">
+        <v>209.1320833333333</v>
+      </c>
+      <c r="D2370" t="n">
+        <v>186.13375</v>
+      </c>
+      <c r="E2370" t="n">
+        <v>194.6033333333333</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B2371" t="n">
+        <v>130.61375</v>
+      </c>
+      <c r="C2371" t="n">
+        <v>130.6104166666666</v>
+      </c>
+      <c r="D2371" t="n">
+        <v>130.6095833333333</v>
+      </c>
+      <c r="E2371" t="n">
+        <v>130.615</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="B2372" t="n">
+        <v>101.94125</v>
+      </c>
+      <c r="C2372" t="n">
+        <v>101.9404166666666</v>
+      </c>
+      <c r="D2372" t="n">
+        <v>101.93875</v>
+      </c>
+      <c r="E2372" t="n">
+        <v>101.9425</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B2373" t="n">
+        <v>132.5666666666666</v>
+      </c>
+      <c r="C2373" t="n">
+        <v>132.5666666666666</v>
+      </c>
+      <c r="D2373" t="n">
+        <v>132.5633333333333</v>
+      </c>
+      <c r="E2373" t="n">
+        <v>132.5691666666666</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B2374" t="n">
+        <v>143.1970833333333</v>
+      </c>
+      <c r="C2374" t="n">
+        <v>143.1975</v>
+      </c>
+      <c r="D2374" t="n">
+        <v>138.7504166666667</v>
+      </c>
+      <c r="E2374" t="n">
+        <v>142.1970833333333</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B2375" t="n">
+        <v>112.4645833333333</v>
+      </c>
+      <c r="C2375" t="n">
+        <v>112.4645833333333</v>
+      </c>
+      <c r="D2375" t="n">
+        <v>112.46125</v>
+      </c>
+      <c r="E2375" t="n">
+        <v>112.4654166666666</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="B2376" t="n">
+        <v>120.21</v>
+      </c>
+      <c r="C2376" t="n">
+        <v>120.2083333333333</v>
+      </c>
+      <c r="D2376" t="n">
+        <v>120.2033333333333</v>
+      </c>
+      <c r="E2376" t="n">
+        <v>120.2108333333333</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="B2377" t="n">
+        <v>138.6595833333333</v>
+      </c>
+      <c r="C2377" t="n">
+        <v>138.65625</v>
+      </c>
+      <c r="D2377" t="n">
+        <v>138.6566666666667</v>
+      </c>
+      <c r="E2377" t="n">
+        <v>138.6616666666666</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="B2378" t="n">
+        <v>91.38833333333332</v>
+      </c>
+      <c r="C2378" t="n">
+        <v>91.38624999999998</v>
+      </c>
+      <c r="D2378" t="n">
+        <v>91.38749999999997</v>
+      </c>
+      <c r="E2378" t="n">
+        <v>91.38999999999999</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="B2379" t="n">
+        <v>85.60416666666664</v>
+      </c>
+      <c r="C2379" t="n">
+        <v>82.70916666666666</v>
+      </c>
+      <c r="D2379" t="n">
+        <v>85.60333333333331</v>
+      </c>
+      <c r="E2379" t="n">
+        <v>85.60624999999999</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="B2380" t="n">
+        <v>110.46375</v>
+      </c>
+      <c r="C2380" t="n">
+        <v>110.4616666666667</v>
+      </c>
+      <c r="D2380" t="n">
+        <v>110.4608333333333</v>
+      </c>
+      <c r="E2380" t="n">
+        <v>110.465</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="B2381" t="n">
+        <v>128.4520833333333</v>
+      </c>
+      <c r="C2381" t="n">
+        <v>128.4483333333333</v>
+      </c>
+      <c r="D2381" t="n">
+        <v>128.4495833333333</v>
+      </c>
+      <c r="E2381" t="n">
+        <v>128.455</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="B2382" t="n">
+        <v>136.5616666666667</v>
+      </c>
+      <c r="C2382" t="n">
+        <v>136.5570833333333</v>
+      </c>
+      <c r="D2382" t="n">
+        <v>136.55875</v>
+      </c>
+      <c r="E2382" t="n">
+        <v>136.56375</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B2383" t="n">
+        <v>124.8254166666667</v>
+      </c>
+      <c r="C2383" t="n">
+        <v>124.8220833333333</v>
+      </c>
+      <c r="D2383" t="n">
+        <v>124.8216666666666</v>
+      </c>
+      <c r="E2383" t="n">
+        <v>124.8275</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="B2384" t="n">
+        <v>132.75375</v>
+      </c>
+      <c r="C2384" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="D2384" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="E2384" t="n">
+        <v>132.7558333333333</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="B2385" t="n">
+        <v>142.8020833333333</v>
+      </c>
+      <c r="C2385" t="n">
+        <v>142.7958333333333</v>
+      </c>
+      <c r="D2385" t="n">
+        <v>142.8008333333333</v>
+      </c>
+      <c r="E2385" t="n">
+        <v>142.8058333333333</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="B2386" t="n">
+        <v>126.7529166666666</v>
+      </c>
+      <c r="C2386" t="n">
+        <v>126.7475</v>
+      </c>
+      <c r="D2386" t="n">
+        <v>126.7504166666667</v>
+      </c>
+      <c r="E2386" t="n">
+        <v>126.7554166666666</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="B2387" t="n">
+        <v>163.1341666666667</v>
+      </c>
+      <c r="C2387" t="n">
+        <v>163.045</v>
+      </c>
+      <c r="D2387" t="n">
+        <v>163.1325</v>
+      </c>
+      <c r="E2387" t="n">
+        <v>163.1383333333333</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="B2388" t="n">
+        <v>151.49</v>
+      </c>
+      <c r="C2388" t="n">
+        <v>151.0570833333333</v>
+      </c>
+      <c r="D2388" t="n">
+        <v>151.4879166666666</v>
+      </c>
+      <c r="E2388" t="n">
+        <v>151.4937499999999</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="B2389" t="n">
+        <v>112.6991666666666</v>
+      </c>
+      <c r="C2389" t="n">
+        <v>112.6958333333333</v>
+      </c>
+      <c r="D2389" t="n">
+        <v>112.6958333333333</v>
+      </c>
+      <c r="E2389" t="n">
+        <v>112.7004166666667</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B2390" t="n">
+        <v>117.8975</v>
+      </c>
+      <c r="C2390" t="n">
+        <v>117.8933333333333</v>
+      </c>
+      <c r="D2390" t="n">
+        <v>117.89375</v>
+      </c>
+      <c r="E2390" t="n">
+        <v>117.8991666666667</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="B2391" t="n">
+        <v>132.8266666666666</v>
+      </c>
+      <c r="C2391" t="n">
+        <v>132.8229166666667</v>
+      </c>
+      <c r="D2391" t="n">
+        <v>132.8216666666667</v>
+      </c>
+      <c r="E2391" t="n">
+        <v>132.8279166666667</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="B2392" t="n">
+        <v>90.50624999999998</v>
+      </c>
+      <c r="C2392" t="n">
+        <v>90.50333333333332</v>
+      </c>
+      <c r="D2392" t="n">
+        <v>90.5045833333333</v>
+      </c>
+      <c r="E2392" t="n">
+        <v>90.50708333333331</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B2393" t="n">
+        <v>97.16166666666665</v>
+      </c>
+      <c r="C2393" t="n">
+        <v>97.15874999999998</v>
+      </c>
+      <c r="D2393" t="n">
+        <v>97.16041666666665</v>
+      </c>
+      <c r="E2393" t="n">
+        <v>97.16333333333331</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="B2394" t="n">
+        <v>129.3654166666667</v>
+      </c>
+      <c r="C2394" t="n">
+        <v>129.3620833333333</v>
+      </c>
+      <c r="D2394" t="n">
+        <v>129.3629166666667</v>
+      </c>
+      <c r="E2394" t="n">
+        <v>129.3670833333333</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="B2395" t="n">
+        <v>161.40875</v>
+      </c>
+      <c r="C2395" t="n">
+        <v>161.4045833333333</v>
+      </c>
+      <c r="D2395" t="n">
+        <v>160.7766666666667</v>
+      </c>
+      <c r="E2395" t="n">
+        <v>160.7833333333333</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="B2396" t="n">
+        <v>184.99375</v>
+      </c>
+      <c r="C2396" t="n">
+        <v>186.5283333333333</v>
+      </c>
+      <c r="D2396" t="n">
+        <v>177.8475</v>
+      </c>
+      <c r="E2396" t="n">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="B2397" t="n">
+        <v>196.24125</v>
+      </c>
+      <c r="C2397" t="n">
+        <v>196.2379166666667</v>
+      </c>
+      <c r="D2397" t="n">
+        <v>196.2354166666667</v>
+      </c>
+      <c r="E2397" t="n">
+        <v>196.2425</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="B2398" t="n">
+        <v>182.2058333333333</v>
+      </c>
+      <c r="C2398" t="n">
+        <v>182.2016666666666</v>
+      </c>
+      <c r="D2398" t="n">
+        <v>182.2020833333333</v>
+      </c>
+      <c r="E2398" t="n">
+        <v>182.2095833333333</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="B2399" t="n">
+        <v>132.7325</v>
+      </c>
+      <c r="C2399" t="n">
+        <v>132.7266666666667</v>
+      </c>
+      <c r="D2399" t="n">
+        <v>132.72875</v>
+      </c>
+      <c r="E2399" t="n">
+        <v>132.735</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="B2400" t="n">
+        <v>95.87583333333332</v>
+      </c>
+      <c r="C2400" t="n">
+        <v>95.87249999999999</v>
+      </c>
+      <c r="D2400" t="n">
+        <v>95.87416666666662</v>
+      </c>
+      <c r="E2400" t="n">
+        <v>95.87749999999998</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B2401" t="n">
+        <v>123.9054166666667</v>
+      </c>
+      <c r="C2401" t="n">
+        <v>123.9020833333333</v>
+      </c>
+      <c r="D2401" t="n">
+        <v>123.9025</v>
+      </c>
+      <c r="E2401" t="n">
+        <v>123.90625</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B2402" t="n">
+        <v>156.4841666666667</v>
+      </c>
+      <c r="C2402" t="n">
+        <v>156.4795833333333</v>
+      </c>
+      <c r="D2402" t="n">
+        <v>156.4804166666666</v>
+      </c>
+      <c r="E2402" t="n">
+        <v>156.4870833333333</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="B2403" t="n">
+        <v>189.7866666666667</v>
+      </c>
+      <c r="C2403" t="n">
+        <v>189.7824999999999</v>
+      </c>
+      <c r="D2403" t="n">
+        <v>188.7375</v>
+      </c>
+      <c r="E2403" t="n">
+        <v>188.7441666666666</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="B2404" t="n">
+        <v>185.415</v>
+      </c>
+      <c r="C2404" t="n">
+        <v>185.4091666666667</v>
+      </c>
+      <c r="D2404" t="n">
+        <v>183.65125</v>
+      </c>
+      <c r="E2404" t="n">
+        <v>184.0020833333333</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B2405" t="n">
+        <v>141.5791666666667</v>
+      </c>
+      <c r="C2405" t="n">
+        <v>141.5733333333333</v>
+      </c>
+      <c r="D2405" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="E2405" t="n">
+        <v>141.58125</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="B2406" t="n">
+        <v>81.78416666666664</v>
+      </c>
+      <c r="C2406" t="n">
+        <v>81.78083333333331</v>
+      </c>
+      <c r="D2406" t="n">
+        <v>81.78208333333332</v>
+      </c>
+      <c r="E2406" t="n">
+        <v>81.78499999999998</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="B2407" t="n">
+        <v>79.43624999999999</v>
+      </c>
+      <c r="C2407" t="n">
+        <v>79.43291666666666</v>
+      </c>
+      <c r="D2407" t="n">
+        <v>79.43416666666666</v>
+      </c>
+      <c r="E2407" t="n">
+        <v>79.43708333333332</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B2408" t="n">
+        <v>108.59375</v>
+      </c>
+      <c r="C2408" t="n">
+        <v>108.5891666666666</v>
+      </c>
+      <c r="D2408" t="n">
+        <v>108.5916666666666</v>
+      </c>
+      <c r="E2408" t="n">
+        <v>108.59625</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="B2409" t="n">
+        <v>124.6304166666666</v>
+      </c>
+      <c r="C2409" t="n">
+        <v>124.6241666666667</v>
+      </c>
+      <c r="D2409" t="n">
+        <v>124.6258333333333</v>
+      </c>
+      <c r="E2409" t="n">
+        <v>124.6325</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B2410" t="n">
+        <v>130.60875</v>
+      </c>
+      <c r="C2410" t="n">
+        <v>130.6025</v>
+      </c>
+      <c r="D2410" t="n">
+        <v>130.0454166666667</v>
+      </c>
+      <c r="E2410" t="n">
+        <v>130.4204166666666</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B2411" t="n">
+        <v>154.26375</v>
+      </c>
+      <c r="C2411" t="n">
+        <v>154.2579166666667</v>
+      </c>
+      <c r="D2411" t="n">
+        <v>154.2604166666667</v>
+      </c>
+      <c r="E2411" t="n">
+        <v>154.2666666666667</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B2412" t="n">
+        <v>145.9979166666666</v>
+      </c>
+      <c r="C2412" t="n">
+        <v>145.6229166666667</v>
+      </c>
+      <c r="D2412" t="n">
+        <v>145.9945833333333</v>
+      </c>
+      <c r="E2412" t="n">
+        <v>146.00125</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="B2413" t="n">
+        <v>104.695</v>
+      </c>
+      <c r="C2413" t="n">
+        <v>104.68875</v>
+      </c>
+      <c r="D2413" t="n">
+        <v>104.69125</v>
+      </c>
+      <c r="E2413" t="n">
+        <v>104.6966666666666</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="B2414" t="n">
+        <v>119.5679166666666</v>
+      </c>
+      <c r="C2414" t="n">
+        <v>119.5679166666666</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>119.5679166666666</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>119.5679166666666</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B2415" t="n">
+        <v>134.4408333333333</v>
+      </c>
+      <c r="C2415" t="n">
+        <v>134.4354166666667</v>
+      </c>
+      <c r="D2415" t="n">
+        <v>134.4375</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>134.4425</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="B2416" t="n">
+        <v>112.3391666666666</v>
+      </c>
+      <c r="C2416" t="n">
+        <v>112.3329166666667</v>
+      </c>
+      <c r="D2416" t="n">
+        <v>112.3345833333333</v>
+      </c>
+      <c r="E2416" t="n">
+        <v>112.34125</v>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="B2417" t="n">
+        <v>121.4325</v>
+      </c>
+      <c r="C2417" t="n">
+        <v>121.42625</v>
+      </c>
+      <c r="D2417" t="n">
+        <v>121.4291666666666</v>
+      </c>
+      <c r="E2417" t="n">
+        <v>121.43625</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="B2418" t="n">
+        <v>180.8683333333333</v>
+      </c>
+      <c r="C2418" t="n">
+        <v>180.8620833333333</v>
+      </c>
+      <c r="D2418" t="n">
+        <v>180.0520833333333</v>
+      </c>
+      <c r="E2418" t="n">
+        <v>180.5933333333333</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B2419" t="n">
+        <v>126.2875</v>
+      </c>
+      <c r="C2419" t="n">
+        <v>126.2804166666667</v>
+      </c>
+      <c r="D2419" t="n">
+        <v>126.2833333333333</v>
+      </c>
+      <c r="E2419" t="n">
+        <v>126.2895833333333</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="B2420" t="n">
+        <v>108.3441666666666</v>
+      </c>
+      <c r="C2420" t="n">
+        <v>108.3383333333333</v>
+      </c>
+      <c r="D2420" t="n">
+        <v>108.34125</v>
+      </c>
+      <c r="E2420" t="n">
+        <v>108.3466666666666</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="B2421" t="n">
+        <v>97.83416666666665</v>
+      </c>
+      <c r="C2421" t="n">
+        <v>97.82958333333329</v>
+      </c>
+      <c r="D2421" t="n">
+        <v>97.83124999999997</v>
+      </c>
+      <c r="E2421" t="n">
+        <v>97.83541666666666</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B2422" t="n">
+        <v>121.0454166666667</v>
+      </c>
+      <c r="C2422" t="n">
+        <v>121.04</v>
+      </c>
+      <c r="D2422" t="n">
+        <v>112.4158333333333</v>
+      </c>
+      <c r="E2422" t="n">
+        <v>117.1745833333333</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="B2423" t="n">
+        <v>122.84875</v>
+      </c>
+      <c r="C2423" t="n">
+        <v>122.84375</v>
+      </c>
+      <c r="D2423" t="n">
+        <v>118.8695833333333</v>
+      </c>
+      <c r="E2423" t="n">
+        <v>120.67875</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="B2424" t="n">
+        <v>133.9754166666667</v>
+      </c>
+      <c r="C2424" t="n">
+        <v>133.9704166666666</v>
+      </c>
+      <c r="D2424" t="n">
+        <v>128.2920833333333</v>
+      </c>
+      <c r="E2424" t="n">
+        <v>131.2241666666667</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="B2425" t="n">
+        <v>128.7954166666667</v>
+      </c>
+      <c r="C2425" t="n">
+        <v>128.79</v>
+      </c>
+      <c r="D2425" t="n">
+        <v>122.8370833333333</v>
+      </c>
+      <c r="E2425" t="n">
+        <v>125.95</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B2426" t="n">
+        <v>127.1029166666667</v>
+      </c>
+      <c r="C2426" t="n">
+        <v>127.0966666666666</v>
+      </c>
+      <c r="D2426" t="n">
+        <v>121.02875</v>
+      </c>
+      <c r="E2426" t="n">
+        <v>124.21875</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="B2427" t="n">
+        <v>116.3483333333333</v>
+      </c>
+      <c r="C2427" t="n">
+        <v>116.3429166666667</v>
+      </c>
+      <c r="D2427" t="n">
+        <v>115.9533333333333</v>
+      </c>
+      <c r="E2427" t="n">
+        <v>116.1758333333333</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B2428" t="n">
+        <v>109.0366666666666</v>
+      </c>
+      <c r="C2428" t="n">
+        <v>109.0304166666667</v>
+      </c>
+      <c r="D2428" t="n">
+        <v>109.0333333333333</v>
+      </c>
+      <c r="E2428" t="n">
+        <v>109.0395833333333</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B2429" t="n">
+        <v>124.9475</v>
+      </c>
+      <c r="C2429" t="n">
+        <v>124.9425</v>
+      </c>
+      <c r="D2429" t="n">
+        <v>114.9591666666666</v>
+      </c>
+      <c r="E2429" t="n">
+        <v>120.7829166666667</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B2430" t="n">
+        <v>134.1558333333334</v>
+      </c>
+      <c r="C2430" t="n">
+        <v>134.15125</v>
+      </c>
+      <c r="D2430" t="n">
+        <v>119.6270833333333</v>
+      </c>
+      <c r="E2430" t="n">
+        <v>126.9983333333333</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B2431" t="n">
+        <v>145.47375</v>
+      </c>
+      <c r="C2431" t="n">
+        <v>145.4691666666667</v>
+      </c>
+      <c r="D2431" t="n">
+        <v>131.6741666666667</v>
+      </c>
+      <c r="E2431" t="n">
+        <v>137.5204166666666</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B2432" t="n">
+        <v>138.8941666666667</v>
+      </c>
+      <c r="C2432" t="n">
+        <v>138.88875</v>
+      </c>
+      <c r="D2432" t="n">
+        <v>132.1295833333333</v>
+      </c>
+      <c r="E2432" t="n">
+        <v>134.8141666666667</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B2433" t="n">
+        <v>136.70625</v>
+      </c>
+      <c r="C2433" t="n">
+        <v>136.7016666666667</v>
+      </c>
+      <c r="D2433" t="n">
+        <v>128.49625</v>
+      </c>
+      <c r="E2433" t="n">
+        <v>132.2783333333334</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B2434" t="n">
+        <v>135.3383333333333</v>
+      </c>
+      <c r="C2434" t="n">
+        <v>135.3325</v>
+      </c>
+      <c r="D2434" t="n">
+        <v>135.335</v>
+      </c>
+      <c r="E2434" t="n">
+        <v>135.3408333333333</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B2435" t="n">
+        <v>124.1241666666666</v>
+      </c>
+      <c r="C2435" t="n">
+        <v>124.1179166666666</v>
+      </c>
+      <c r="D2435" t="n">
+        <v>124.12</v>
+      </c>
+      <c r="E2435" t="n">
+        <v>124.1258333333333</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B2436" t="n">
+        <v>241.7249999999999</v>
+      </c>
+      <c r="C2436" t="n">
+        <v>241.7195833333333</v>
+      </c>
+      <c r="D2436" t="n">
+        <v>238.89375</v>
+      </c>
+      <c r="E2436" t="n">
+        <v>240.7616666666666</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B2437" t="n">
+        <v>239.9183333333333</v>
+      </c>
+      <c r="C2437" t="n">
+        <v>239.9120833333333</v>
+      </c>
+      <c r="D2437" t="n">
+        <v>235.8245833333333</v>
+      </c>
+      <c r="E2437" t="n">
+        <v>237.92625</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="B2438" t="n">
+        <v>212.8154166666666</v>
+      </c>
+      <c r="C2438" t="n">
+        <v>212.8091666666667</v>
+      </c>
+      <c r="D2438" t="n">
+        <v>212.81125</v>
+      </c>
+      <c r="E2438" t="n">
+        <v>212.8187499999999</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B2439" t="n">
+        <v>154.2904166666667</v>
+      </c>
+      <c r="C2439" t="n">
+        <v>154.285</v>
+      </c>
+      <c r="D2439" t="n">
+        <v>152.6266666666667</v>
+      </c>
+      <c r="E2439" t="n">
+        <v>153.7258333333333</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B2440" t="n">
+        <v>168.9308333333333</v>
+      </c>
+      <c r="C2440" t="n">
+        <v>168.9233333333333</v>
+      </c>
+      <c r="D2440" t="n">
+        <v>166.0508333333333</v>
+      </c>
+      <c r="E2440" t="n">
+        <v>167.9525</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B2441" t="n">
+        <v>146.4108333333333</v>
+      </c>
+      <c r="C2441" t="n">
+        <v>146.4108333333333</v>
+      </c>
+      <c r="D2441" t="n">
+        <v>146.4108333333333</v>
+      </c>
+      <c r="E2441" t="n">
+        <v>146.4108333333333</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B2442" t="n">
+        <v>118.0458333333333</v>
+      </c>
+      <c r="C2442" t="n">
+        <v>118.0395833333333</v>
+      </c>
+      <c r="D2442" t="n">
+        <v>118.0425</v>
+      </c>
+      <c r="E2442" t="n">
+        <v>118.04875</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B2443" t="n">
+        <v>113.6845833333333</v>
+      </c>
+      <c r="C2443" t="n">
+        <v>113.67875</v>
+      </c>
+      <c r="D2443" t="n">
+        <v>113.6808333333333</v>
+      </c>
+      <c r="E2443" t="n">
+        <v>113.6870833333333</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B2444" t="n">
+        <v>97.78541666666665</v>
+      </c>
+      <c r="C2444" t="n">
+        <v>97.78166666666665</v>
+      </c>
+      <c r="D2444" t="n">
+        <v>97.78249999999998</v>
+      </c>
+      <c r="E2444" t="n">
+        <v>97.78749999999998</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B2445" t="n">
+        <v>114.10875</v>
+      </c>
+      <c r="C2445" t="n">
+        <v>114.1029166666666</v>
+      </c>
+      <c r="D2445" t="n">
+        <v>114.1058333333333</v>
+      </c>
+      <c r="E2445" t="n">
+        <v>114.1116666666666</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B2446" t="n">
+        <v>142.6766666666666</v>
+      </c>
+      <c r="C2446" t="n">
+        <v>142.6708333333333</v>
+      </c>
+      <c r="D2446" t="n">
+        <v>142.6733333333333</v>
+      </c>
+      <c r="E2446" t="n">
+        <v>142.68</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B2447" t="n">
+        <v>179.1458333333333</v>
+      </c>
+      <c r="C2447" t="n">
+        <v>179.1395833333333</v>
+      </c>
+      <c r="D2447" t="n">
+        <v>179.1425</v>
+      </c>
+      <c r="E2447" t="n">
+        <v>179.14875</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B2448" t="n">
+        <v>130.68875</v>
+      </c>
+      <c r="C2448" t="n">
+        <v>130.6825</v>
+      </c>
+      <c r="D2448" t="n">
+        <v>130.685</v>
+      </c>
+      <c r="E2448" t="n">
+        <v>130.69125</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B2449" t="n">
+        <v>87.63499999999999</v>
+      </c>
+      <c r="C2449" t="n">
+        <v>87.63208333333331</v>
+      </c>
+      <c r="D2449" t="n">
+        <v>87.63374999999998</v>
+      </c>
+      <c r="E2449" t="n">
+        <v>87.63708333333334</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B2450" t="n">
+        <v>90.97166666666665</v>
+      </c>
+      <c r="C2450" t="n">
+        <v>90.96833333333331</v>
+      </c>
+      <c r="D2450" t="n">
+        <v>90.96958333333332</v>
+      </c>
+      <c r="E2450" t="n">
+        <v>90.97249999999998</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B2451" t="n">
+        <v>94.04374999999999</v>
+      </c>
+      <c r="C2451" t="n">
+        <v>94.04124999999999</v>
+      </c>
+      <c r="D2451" t="n">
+        <v>94.04208333333332</v>
+      </c>
+      <c r="E2451" t="n">
+        <v>94.04541666666665</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B2452" t="n">
+        <v>119.08875</v>
+      </c>
+      <c r="C2452" t="n">
+        <v>110.4908333333333</v>
+      </c>
+      <c r="D2452" t="n">
+        <v>119.0854166666667</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>119.09</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B2453" t="n">
+        <v>95.13749999999997</v>
+      </c>
+      <c r="C2453" t="n">
+        <v>94.67083333333331</v>
+      </c>
+      <c r="D2453" t="n">
+        <v>95.13499999999998</v>
+      </c>
+      <c r="E2453" t="n">
+        <v>95.13833333333332</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B2454" t="n">
+        <v>89.55958333333332</v>
+      </c>
+      <c r="C2454" t="n">
+        <v>89.08249999999997</v>
+      </c>
+      <c r="D2454" t="n">
+        <v>89.55791666666666</v>
+      </c>
+      <c r="E2454" t="n">
+        <v>89.56166666666667</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B2455" t="n">
+        <v>74.33541666666665</v>
+      </c>
+      <c r="C2455" t="n">
+        <v>69.38499999999998</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>74.33374999999998</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>74.33708333333333</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B2456" t="n">
+        <v>77.12083333333332</v>
+      </c>
+      <c r="C2456" t="n">
+        <v>75.33374999999998</v>
+      </c>
+      <c r="D2456" t="n">
+        <v>77.11916666666666</v>
+      </c>
+      <c r="E2456" t="n">
+        <v>77.12249999999999</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B2457" t="n">
+        <v>116.72875</v>
+      </c>
+      <c r="C2457" t="n">
+        <v>116.725</v>
+      </c>
+      <c r="D2457" t="n">
+        <v>116.7270833333333</v>
+      </c>
+      <c r="E2457" t="n">
+        <v>116.73125</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B2458" t="n">
+        <v>186.8670833333333</v>
+      </c>
+      <c r="C2458" t="n">
+        <v>186.8620833333333</v>
+      </c>
+      <c r="D2458" t="n">
+        <v>186.8629166666666</v>
+      </c>
+      <c r="E2458" t="n">
+        <v>186.86875</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B2459" t="n">
+        <v>199.7933333333333</v>
+      </c>
+      <c r="C2459" t="n">
+        <v>199.7870833333333</v>
+      </c>
+      <c r="D2459" t="n">
+        <v>199.7908333333333</v>
+      </c>
+      <c r="E2459" t="n">
+        <v>199.79625</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B2460" t="n">
+        <v>107.185</v>
+      </c>
+      <c r="C2460" t="n">
+        <v>96.19958333333331</v>
+      </c>
+      <c r="D2460" t="n">
+        <v>107.1820833333333</v>
+      </c>
+      <c r="E2460" t="n">
+        <v>107.1883333333333</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B2461" t="n">
+        <v>106.6075</v>
+      </c>
+      <c r="C2461" t="n">
+        <v>101.7525</v>
+      </c>
+      <c r="D2461" t="n">
+        <v>106.6041666666666</v>
+      </c>
+      <c r="E2461" t="n">
+        <v>106.6095833333333</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B2462" t="n">
+        <v>75.07083333333331</v>
+      </c>
+      <c r="C2462" t="n">
+        <v>70.99458333333331</v>
+      </c>
+      <c r="D2462" t="n">
+        <v>75.06958333333331</v>
+      </c>
+      <c r="E2462" t="n">
+        <v>75.07499999999997</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="B2463" t="n">
+        <v>71.82333333333331</v>
+      </c>
+      <c r="C2463" t="n">
+        <v>68.27791666666664</v>
+      </c>
+      <c r="D2463" t="n">
+        <v>71.82083333333331</v>
+      </c>
+      <c r="E2463" t="n">
+        <v>71.82541666666664</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B2464" t="n">
+        <v>105.2716666666667</v>
+      </c>
+      <c r="C2464" t="n">
+        <v>99.01041666666664</v>
+      </c>
+      <c r="D2464" t="n">
+        <v>105.2679166666667</v>
+      </c>
+      <c r="E2464" t="n">
+        <v>105.27375</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B2465" t="n">
+        <v>122.4066666666667</v>
+      </c>
+      <c r="C2465" t="n">
+        <v>114.8225</v>
+      </c>
+      <c r="D2465" t="n">
+        <v>122.4020833333333</v>
+      </c>
+      <c r="E2465" t="n">
+        <v>122.4083333333333</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B2466" t="n">
+        <v>135.2458333333333</v>
+      </c>
+      <c r="C2466" t="n">
+        <v>127.8575</v>
+      </c>
+      <c r="D2466" t="n">
+        <v>124.9295833333333</v>
+      </c>
+      <c r="E2466" t="n">
+        <v>135.2466666666667</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="B2467" t="n">
+        <v>123.5204166666667</v>
+      </c>
+      <c r="C2467" t="n">
+        <v>121.9416666666667</v>
+      </c>
+      <c r="D2467" t="n">
+        <v>117.7566666666667</v>
+      </c>
+      <c r="E2467" t="n">
+        <v>122.57125</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="B2468" t="n">
+        <v>170.5883333333333</v>
+      </c>
+      <c r="C2468" t="n">
+        <v>168.9695833333333</v>
+      </c>
+      <c r="D2468" t="n">
+        <v>170.5833333333333</v>
+      </c>
+      <c r="E2468" t="n">
+        <v>170.5920833333333</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="B2469" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2469" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2469" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2469" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="B2470" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2470" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2470" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2470" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B2471" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2471" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2471" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2471" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B2472" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2472" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2472" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2472" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="B2473" t="n">
+        <v>57.62166666666663</v>
+      </c>
+      <c r="C2473" t="n">
+        <v>57.62124999999997</v>
+      </c>
+      <c r="D2473" t="n">
+        <v>57.62124999999997</v>
+      </c>
+      <c r="E2473" t="n">
+        <v>57.62166666666663</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B2474" t="n">
+        <v>59.48666666666663</v>
+      </c>
+      <c r="C2474" t="n">
+        <v>59.48624999999996</v>
+      </c>
+      <c r="D2474" t="n">
+        <v>59.4858333333333</v>
+      </c>
+      <c r="E2474" t="n">
+        <v>59.48666666666663</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B2475" t="n">
+        <v>58.17124999999998</v>
+      </c>
+      <c r="C2475" t="n">
+        <v>58.17083333333331</v>
+      </c>
+      <c r="D2475" t="n">
+        <v>58.12208333333331</v>
+      </c>
+      <c r="E2475" t="n">
+        <v>58.17124999999998</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="B2476" t="n">
+        <v>58.8070833333333</v>
+      </c>
+      <c r="C2476" t="n">
+        <v>58.61999999999997</v>
+      </c>
+      <c r="D2476" t="n">
+        <v>58.80541666666664</v>
+      </c>
+      <c r="E2476" t="n">
+        <v>58.8083333333333</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B2477" t="n">
+        <v>57.95958333333331</v>
+      </c>
+      <c r="C2477" t="n">
+        <v>57.89374999999998</v>
+      </c>
+      <c r="D2477" t="n">
+        <v>57.95874999999997</v>
+      </c>
+      <c r="E2477" t="n">
+        <v>57.96124999999997</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="B2478" t="n">
+        <v>58.23958333333332</v>
+      </c>
+      <c r="C2478" t="n">
+        <v>58.05749999999998</v>
+      </c>
+      <c r="D2478" t="n">
+        <v>58.23958333333332</v>
+      </c>
+      <c r="E2478" t="n">
+        <v>58.24166666666665</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="B2479" t="n">
+        <v>77.79041666666664</v>
+      </c>
+      <c r="C2479" t="n">
+        <v>77.78791666666665</v>
+      </c>
+      <c r="D2479" t="n">
+        <v>77.78874999999996</v>
+      </c>
+      <c r="E2479" t="n">
+        <v>77.79083333333331</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="B2480" t="n">
+        <v>100.3120833333333</v>
+      </c>
+      <c r="C2480" t="n">
+        <v>100.3091666666667</v>
+      </c>
+      <c r="D2480" t="n">
+        <v>100.31</v>
+      </c>
+      <c r="E2480" t="n">
+        <v>100.3125</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B2481" t="n">
+        <v>318.9166666666667</v>
+      </c>
+      <c r="C2481" t="n">
+        <v>318.85875</v>
+      </c>
+      <c r="D2481" t="n">
+        <v>318.9158333333334</v>
+      </c>
+      <c r="E2481" t="n">
+        <v>318.92</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="B2482" t="n">
+        <v>170.9383333333333</v>
+      </c>
+      <c r="C2482" t="n">
+        <v>170.915</v>
+      </c>
+      <c r="D2482" t="n">
+        <v>170.9366666666667</v>
+      </c>
+      <c r="E2482" t="n">
+        <v>170.9416666666666</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B2483" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2483" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2483" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2483" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B2484" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2484" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2484" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2484" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="B2485" t="n">
+        <v>150.5220833333333</v>
+      </c>
+      <c r="C2485" t="n">
+        <v>150.5208333333333</v>
+      </c>
+      <c r="D2485" t="n">
+        <v>150.5216666666666</v>
+      </c>
+      <c r="E2485" t="n">
+        <v>150.5225</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="B2486" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2486" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2486" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2486" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="B2487" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2487" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2487" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2487" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="B2488" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B2489" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B2490" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B2491" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="B2492" t="n">
+        <v>161.42875</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>161.4270833333333</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>161.4283333333333</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>161.4291666666666</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="B2493" t="n">
+        <v>87.33583333333331</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>87.33374999999999</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>87.33416666666665</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>87.33583333333331</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B2494" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="B2495" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>57.30999999999997</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>57.30999999999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
